--- a/rapport_historique_projet_biointeraction.xlsx
+++ b/rapport_historique_projet_biointeraction.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Synthese" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Journal detaille'!$A$2:$E$133</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -31,139 +30,139 @@
     <font>
       <name val="DM Serif Display"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="30"/>
     </font>
     <font>
       <name val="DM Serif Display"/>
-      <color rgb="001B1F1D"/>
+      <color rgb="FF1B1F1D"/>
       <sz val="17"/>
     </font>
     <font>
       <name val="DM Sans"/>
-      <color rgb="006E6E6E"/>
+      <color rgb="FF6E6E6E"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Serif Display"/>
       <b val="1"/>
-      <color rgb="0015623A"/>
+      <color rgb="FF15623A"/>
       <sz val="22"/>
     </font>
     <font>
       <name val="DM Sans"/>
-      <color rgb="006E6E6E"/>
+      <color rgb="FF6E6E6E"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="0015623A"/>
+      <color rgb="FF15623A"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="001F8A52"/>
+      <color rgb="FF1F8A52"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Sans"/>
-      <color rgb="001B1F1D"/>
+      <color rgb="FF1B1F1D"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="00196D43"/>
+      <color rgb="FF196D43"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="006E6E6E"/>
+      <color rgb="FF6E6E6E"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="0015623A"/>
+      <color rgb="FF15623A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="000F4226"/>
+      <color rgb="FF0F4226"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="00A9ADAA"/>
+      <color rgb="FFA9ADAA"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <i val="1"/>
-      <color rgb="00A9ADAA"/>
+      <color rgb="FFA9ADAA"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="DM Serif Display"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="00A9ADAA"/>
+      <color rgb="FFA9ADAA"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="DM Sans"/>
-      <color rgb="001B1F1D"/>
+      <color rgb="FF1B1F1D"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Consolas"/>
-      <color rgb="00A9ADAA"/>
+      <color rgb="FFA9ADAA"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="006E6E6E"/>
+      <color rgb="FF6E6E6E"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="00196D43"/>
+      <color rgb="FF196D43"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="001F8A52"/>
+      <color rgb="FF1F8A52"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="000F4226"/>
+      <color rgb="FF0F4226"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="DM Sans"/>
       <b val="1"/>
-      <color rgb="0015623A"/>
+      <color rgb="FF15623A"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -176,27 +175,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0029A864"/>
+        <fgColor rgb="FF29A864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDF8F1"/>
+        <fgColor rgb="FFEDF8F1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00196D43"/>
+        <fgColor rgb="FF196D43"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0015623A"/>
+        <fgColor rgb="FF15623A"/>
       </patternFill>
     </fill>
   </fills>
@@ -210,34 +209,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00E5E3DC"/>
+        <color rgb="FFE5E3DC"/>
       </left>
       <right style="thin">
-        <color rgb="00E5E3DC"/>
+        <color rgb="FFE5E3DC"/>
       </right>
       <top style="thin">
-        <color rgb="00E5E3DC"/>
+        <color rgb="FFE5E3DC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E5E3DC"/>
+        <color rgb="FFE5E3DC"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -275,12 +265,6 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -346,9 +330,26 @@
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -712,340 +713,309 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" style="36" min="1" max="1"/>
+    <col width="26" customWidth="1" style="36" min="2" max="2"/>
+    <col width="16" customWidth="1" style="36" min="3" max="4"/>
+    <col width="20" customWidth="1" style="36" min="5" max="5"/>
+    <col width="18" customWidth="1" style="36" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="36">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>BioInteraction®</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    </row>
+    <row r="2" ht="18" customHeight="1" s="36"/>
+    <row r="3" ht="18" customHeight="1" s="36"/>
+    <row r="4" ht="18" customHeight="1" s="36"/>
+    <row r="5" ht="26.1" customHeight="1" s="36">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Historique des modifications du site web</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Periode : 18 mai 2026  →  9 juin 2026  ·  Distribution medicale, Alger  ·  Genere le 9 juin 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>Periode : 18 mai 2026  →  10 juin 2026  ·  Distribution medicale, Alger  ·  Genere le 10 juin 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="33.95" customHeight="1" s="36">
+      <c r="B8" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>23 jours</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="6" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>24 jours</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21.95" customHeight="1" s="36">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Commits au total</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Changements retenus</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Redeploiements exclus</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Duree du projet</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="7" t="inlineStr">
+    <row r="12" ht="15.75" customHeight="1" s="36">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Repartition par type</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Repartition par zone</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Catalogue</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Amelioration</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Compte/Auth</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>Catalogue</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Amelioration</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>Compte/Auth</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>19</v>
-      </c>
     </row>
     <row r="16">
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="C16" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>13</v>
+      <c r="F16" s="6" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="8" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Refonte/Design</t>
         </is>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>Transverse</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="6" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Donnees/Catalogue</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Accueil</t>
         </is>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="8" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="6" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Infra/Chore</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Design/UI</t>
         </is>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="F21" s="8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="22">
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="23">
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="F23" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="24">
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Reactifs</t>
         </is>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="6" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="25">
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Partenaires</t>
         </is>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="26">
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>Profil</t>
         </is>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="F26" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>biointeraction.dz  ·  support@biointeractiondz.com  ·  SAV : +213.770.74.72.50</t>
         </is>
@@ -1066,3590 +1036,3694 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E137"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="88" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" style="36" min="1" max="1"/>
+    <col width="18" customWidth="1" style="36" min="2" max="2"/>
+    <col width="16" customWidth="1" style="36" min="3" max="3"/>
+    <col width="88" customWidth="1" style="36" min="4" max="4"/>
+    <col width="12" customWidth="1" style="36" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+    <row r="1" ht="26.1" customHeight="1" s="36">
+      <c r="A1" s="41" t="inlineStr">
         <is>
           <t>BioInteraction®  —  Journal detaille des changements</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+    </row>
+    <row r="2" ht="20.1" customHeight="1" s="36">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C2" s="20" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>Commit</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Infra/Chore</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Initialisation du projet : migration vers Next.js 16 (App Router).</t>
         </is>
       </c>
-      <c r="E3" s="25" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>339d057</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>Infra/Chore</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Ajout du modele .env.example et ajustement du .gitignore.</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>bbb5773</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>Correction de l'initialisation Resend (dans le handler) pour eviter une erreur de build liee a la cle API.</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>fb21489</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Donnees/Catalogue</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>Ajout des images d'equipements extraites du catalogue PDF.</t>
         </is>
       </c>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>5202283</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>Correction de l'affichage des images d'equipements (balise img au lieu de next/image fill).</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>d3f797d</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Donnees/Catalogue</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>Remplacement des images PDF par des photos fabricant web (800x800 JPEG).</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>317c46f</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>Adaptation des images d'equipements pour remplir les cartes et la galerie.</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>c0c2da7</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+    <row r="10" ht="27" customHeight="1" s="36">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Donnees/Catalogue</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>Reconstruction de 11 images d'equipements depuis des extraits PDF haute resolution (recadrage carre).</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>7818185</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>Ajout du flux de validation administrateur des comptes utilisateurs.</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>cab9ee8</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>Notification de l'administrateur par email lors d'une nouvelle inscription.</t>
         </is>
       </c>
-      <c r="E12" s="30" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>7866179</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>Utilisation de l'expediteur resend.dev en attendant la verification du domaine.</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>f152d8f</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D14" s="29" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>Page admin : recuperation des utilisateurs cote client pour eviter un index composite Firestore.</t>
         </is>
       </c>
-      <c r="E14" s="30" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>65fb221</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>Page admin : route serveur firebase-admin pour contourner les regles Firestore.</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>af8c36f</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B16" s="36" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D16" s="29" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>Correction de l'init firebase-admin (normalisation des sauts de ligne de la cle privee, details d'erreur).</t>
         </is>
       </c>
-      <c r="E16" s="30" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>b41755e</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>Affichage du message d'erreur API reel sur la page admin.</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>2ed5d33</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>Infra/Chore</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D18" s="29" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>Ajout d'un endpoint de diagnostic pour firebase-admin.</t>
         </is>
       </c>
-      <c r="E18" s="30" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>56b2f2b</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>Variables d'environnement separees pour les identifiants firebase-admin.</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>a442efa</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B20" s="36" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C20" s="28" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D20" s="29" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>Suppression des guillemets autour de la variable FIREBASE_PRIVATE_KEY.</t>
         </is>
       </c>
-      <c r="E20" s="30" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>7ce7f97</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>Compte de service encode en base64 pour eviter les problemes d'echappement de variables.</t>
         </is>
       </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>52449f3</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C22" s="28" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D22" s="29" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>Retour de la page admin au SDK Firestore client.</t>
         </is>
       </c>
-      <c r="E22" s="30" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>3cf6313</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B23" s="31" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>Suppression de routes API firebase-admin inutilisees qui cassaient le build.</t>
         </is>
       </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>f3599d4</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D24" s="29" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>Ajout de l'etape de verification d'email avant l'approbation admin.</t>
         </is>
       </c>
-      <c r="E24" s="30" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>aa6ce7c</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B25" s="33" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>Notification de l'admin seulement apres verification de l'email (et non a l'inscription).</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>7ea1e25</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C26" s="28" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>Remplacement de l'email de verification Firebase par un email personnalise via Resend.</t>
         </is>
       </c>
-      <c r="E26" s="30" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>78ee3b9</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D27" s="18" t="inlineStr">
         <is>
           <t>Utilisation du domaine verifie noreply@biointeractiondz.com pour les emails Resend.</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E27" s="19" t="inlineStr">
         <is>
           <t>90b7782</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>Refonte/Design</t>
         </is>
       </c>
-      <c r="C28" s="28" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D28" s="29" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>Harmonisation de la page /auth/action avec le systeme de design du site.</t>
         </is>
       </c>
-      <c r="E28" s="30" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>44435db</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>Profil</t>
         </is>
       </c>
-      <c r="D29" s="24" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>Ajout de la page profil utilisateur (photo, nom, telephone, societe).</t>
         </is>
       </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="E29" s="19" t="inlineStr">
         <is>
           <t>96246b5</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B30" s="32" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>Donnees/Catalogue</t>
         </is>
       </c>
-      <c r="C30" s="28" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="D30" s="29" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>Ajout des images produits au catalogue equipements (17 articles).</t>
         </is>
       </c>
-      <c r="E30" s="30" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>ace1a78</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>Mise au format carre des blocs image du catalogue (object-cover).</t>
         </is>
       </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>ef1f710</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B32" s="32" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C32" s="28" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D32" s="29" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>Mise au format carre du bloc image de la fiche produit.</t>
         </is>
       </c>
-      <c r="E32" s="30" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>1ecad17</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B33" s="34" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>Ajout d'une lightbox au clic sur l'image de la fiche produit.</t>
         </is>
       </c>
-      <c r="E33" s="25" t="inlineStr">
+      <c r="E33" s="19" t="inlineStr">
         <is>
           <t>85e634f</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B34" s="32" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C34" s="28" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D34" s="29" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>Animation de zoom subtile au survol des images du catalogue et des fiches.</t>
         </is>
       </c>
-      <c r="E34" s="30" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>31c658f</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B35" s="38" t="inlineStr">
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>Transverse</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D35" s="18" t="inlineStr">
         <is>
           <t>Corrections de bugs, suppression de code mort et durcissement de la securite des emails.</t>
         </is>
       </c>
-      <c r="E35" s="25" t="inlineStr">
+      <c r="E35" s="19" t="inlineStr">
         <is>
           <t>c561b88</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B36" s="36" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C36" s="28" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D36" s="29" t="inlineStr">
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>Correction de la redirection « reactifs compatibles » qui contournait les pages d'atterrissage.</t>
         </is>
       </c>
-      <c r="E36" s="30" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>0cd9795</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B37" s="34" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C37" s="23" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D37" s="24" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>Ajout du bouton « Voir tous les reactifs » sur la page d'atterrissage.</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="E37" s="19" t="inlineStr">
         <is>
           <t>2a1dbd3</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="29" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C38" s="28" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="D38" s="29" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>Ajout du systeme de blog complet : editeur admin, acces protege, flux brouillon/publication.</t>
         </is>
       </c>
-      <c r="E38" s="30" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>bf3093f</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B39" s="33" t="inlineStr">
+      <c r="B39" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="D39" s="24" t="inlineStr">
+      <c r="D39" s="18" t="inlineStr">
         <is>
           <t>Slug d'article genere automatiquement depuis le titre et passe en lecture seule.</t>
         </is>
       </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="E39" s="19" t="inlineStr">
         <is>
           <t>a8b0024</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B40" s="35" t="inlineStr">
+      <c r="B40" s="29" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C40" s="28" t="inlineStr">
+      <c r="C40" s="22" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D40" s="29" t="inlineStr">
+      <c r="D40" s="23" t="inlineStr">
         <is>
           <t>Ajout du systeme de gestion des roles (admin/utilisateur) dans le panneau admin.</t>
         </is>
       </c>
-      <c r="E40" s="30" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>fbcb8f5</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B41" s="33" t="inlineStr">
+      <c r="B41" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C41" s="23" t="inlineStr">
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>Transverse</t>
         </is>
       </c>
-      <c r="D41" s="24" t="inlineStr">
+      <c r="D41" s="18" t="inlineStr">
         <is>
           <t>Mises a jour diverses d'interface et de contenu.</t>
         </is>
       </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="E41" s="19" t="inlineStr">
         <is>
           <t>26428e6</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="26" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B42" s="32" t="inlineStr">
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C42" s="28" t="inlineStr">
+      <c r="C42" s="22" t="inlineStr">
         <is>
           <t>Accueil</t>
         </is>
       </c>
-      <c r="D42" s="29" t="inlineStr">
+      <c r="D42" s="23" t="inlineStr">
         <is>
           <t>Mise a jour du texte du badge du Hero.</t>
         </is>
       </c>
-      <c r="E42" s="30" t="inlineStr">
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>a5854c9</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="21" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B43" s="33" t="inlineStr">
+      <c r="B43" s="27" t="inlineStr">
         <is>
           <t>Donnees/Catalogue</t>
         </is>
       </c>
-      <c r="C43" s="23" t="inlineStr">
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D43" s="24" t="inlineStr">
+      <c r="D43" s="18" t="inlineStr">
         <is>
           <t>Ajout de l'image du produit BioCLIA 1900.</t>
         </is>
       </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="E43" s="19" t="inlineStr">
         <is>
           <t>356dc5c</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="26" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B44" s="36" t="inlineStr">
+      <c r="B44" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C44" s="28" t="inlineStr">
+      <c r="C44" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D44" s="29" t="inlineStr">
+      <c r="D44" s="23" t="inlineStr">
         <is>
           <t>Correction de l'extension de l'image BioCLIA 1900 (jpg vers webp).</t>
         </is>
       </c>
-      <c r="E44" s="30" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>b215eac</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B45" s="33" t="inlineStr">
+      <c r="B45" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C45" s="23" t="inlineStr">
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D45" s="24" t="inlineStr">
+      <c r="D45" s="18" t="inlineStr">
         <is>
           <t>Remplacement des instruments BioCLIA en allergie par un bloc d'information reactifs CLIA.</t>
         </is>
       </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="E45" s="19" t="inlineStr">
         <is>
           <t>de1ffb7</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="26" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B46" s="36" t="inlineStr">
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C46" s="28" t="inlineStr">
+      <c r="C46" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D46" s="29" t="inlineStr">
+      <c r="D46" s="23" t="inlineStr">
         <is>
           <t>Retour des entrees BioCLIA allergie au format instrument.</t>
         </is>
       </c>
-      <c r="E46" s="30" t="inlineStr">
+      <c r="E46" s="24" t="inlineStr">
         <is>
           <t>a8b7ec6</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B47" s="33" t="inlineStr">
+      <c r="B47" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C47" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D47" s="24" t="inlineStr">
+      <c r="D47" s="18" t="inlineStr">
         <is>
           <t>Retrait des instruments BioCLIA de la categorie allergie.</t>
         </is>
       </c>
-      <c r="E47" s="25" t="inlineStr">
+      <c r="E47" s="19" t="inlineStr">
         <is>
           <t>44ce09d</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="26" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B48" s="32" t="inlineStr">
+      <c r="B48" s="26" t="inlineStr">
         <is>
           <t>Donnees/Catalogue</t>
         </is>
       </c>
-      <c r="C48" s="28" t="inlineStr">
+      <c r="C48" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D48" s="29" t="inlineStr">
+      <c r="D48" s="23" t="inlineStr">
         <is>
           <t>Ajout de 78 reactifs IgE BioCLIA a la categorie allergie.</t>
         </is>
       </c>
-      <c r="E48" s="30" t="inlineStr">
+      <c r="E48" s="24" t="inlineStr">
         <is>
           <t>c86208f</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B49" s="33" t="inlineStr">
+      <c r="B49" s="27" t="inlineStr">
         <is>
           <t>Donnees/Catalogue</t>
         </is>
       </c>
-      <c r="C49" s="23" t="inlineStr">
+      <c r="C49" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D49" s="24" t="inlineStr">
+      <c r="D49" s="18" t="inlineStr">
         <is>
           <t>Ajout des sections reactifs BioCLIA auto-immunite et allergie.</t>
         </is>
       </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="E49" s="19" t="inlineStr">
         <is>
           <t>fba9e6a</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="26" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B50" s="36" t="inlineStr">
+      <c r="B50" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C50" s="28" t="inlineStr">
+      <c r="C50" s="22" t="inlineStr">
         <is>
           <t>Transverse</t>
         </is>
       </c>
-      <c r="D50" s="29" t="inlineStr">
+      <c r="D50" s="23" t="inlineStr">
         <is>
           <t>Corrections et optimisations : gestion d'erreurs, coquilles, images en chargement differe.</t>
         </is>
       </c>
-      <c r="E50" s="30" t="inlineStr">
+      <c r="E50" s="24" t="inlineStr">
         <is>
           <t>fcd96cd</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="21" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B51" s="34" t="inlineStr">
+      <c r="B51" s="28" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C51" s="23" t="inlineStr">
+      <c r="C51" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D51" s="24" t="inlineStr">
+      <c r="D51" s="18" t="inlineStr">
         <is>
           <t>Ajout des fiches techniques avec boutons de telechargement (ERBA XSYS).</t>
         </is>
       </c>
-      <c r="E51" s="25" t="inlineStr">
+      <c r="E51" s="19" t="inlineStr">
         <is>
           <t>89cd8e3</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B52" s="32" t="inlineStr">
+      <c r="B52" s="26" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C52" s="28" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D52" s="29" t="inlineStr">
+      <c r="D52" s="23" t="inlineStr">
         <is>
           <t>Conservation des seules notices IFU dans les fiches techniques (retrait du protocole AP).</t>
         </is>
       </c>
-      <c r="E52" s="30" t="inlineStr">
+      <c r="E52" s="24" t="inlineStr">
         <is>
           <t>b3de84c</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="21" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B53" s="34" t="inlineStr">
+      <c r="B53" s="28" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C53" s="23" t="inlineStr">
+      <c r="C53" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D53" s="24" t="inlineStr">
+      <c r="D53" s="18" t="inlineStr">
         <is>
           <t>Ajout des notices LDBIO avec bouton de telechargement (17 reactifs parasitologie).</t>
         </is>
       </c>
-      <c r="E53" s="25" t="inlineStr">
+      <c r="E53" s="19" t="inlineStr">
         <is>
           <t>4c032c4</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="26" t="inlineStr">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B54" s="35" t="inlineStr">
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C54" s="28" t="inlineStr">
+      <c r="C54" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D54" s="29" t="inlineStr">
+      <c r="D54" s="23" t="inlineStr">
         <is>
           <t>Ajout des notices IFU Medipan via proxy API (91 produits Generic Assays).</t>
         </is>
       </c>
-      <c r="E54" s="30" t="inlineStr">
+      <c r="E54" s="24" t="inlineStr">
         <is>
           <t>3166c19</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="21" t="inlineStr">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B55" s="33" t="inlineStr">
+      <c r="B55" s="27" t="inlineStr">
         <is>
           <t>Donnees/Catalogue</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
+      <c r="C55" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D55" s="24" t="inlineStr">
+      <c r="D55" s="18" t="inlineStr">
         <is>
           <t>Extension de la couverture des notices de 118 a 253 produits (+135).</t>
         </is>
       </c>
-      <c r="E55" s="25" t="inlineStr">
+      <c r="E55" s="19" t="inlineStr">
         <is>
           <t>57a605a</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="26" t="inlineStr">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B56" s="32" t="inlineStr">
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>Donnees/Catalogue</t>
         </is>
       </c>
-      <c r="C56" s="28" t="inlineStr">
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>Reactifs</t>
         </is>
       </c>
-      <c r="D56" s="29" t="inlineStr">
+      <c r="D56" s="23" t="inlineStr">
         <is>
           <t>Ajout des images produits aux 481 reactifs.</t>
         </is>
       </c>
-      <c r="E56" s="30" t="inlineStr">
+      <c r="E56" s="24" t="inlineStr">
         <is>
           <t>4d1a697</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="21" t="inlineStr">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B57" s="33" t="inlineStr">
+      <c r="B57" s="27" t="inlineStr">
         <is>
           <t>Donnees/Catalogue</t>
         </is>
       </c>
-      <c r="C57" s="23" t="inlineStr">
+      <c r="C57" s="17" t="inlineStr">
         <is>
           <t>Reactifs</t>
         </is>
       </c>
-      <c r="D57" s="24" t="inlineStr">
+      <c r="D57" s="18" t="inlineStr">
         <is>
           <t>Remplacement des images generiques par de vraies photos pour les 481 produits.</t>
         </is>
       </c>
-      <c r="E57" s="25" t="inlineStr">
+      <c r="E57" s="19" t="inlineStr">
         <is>
           <t>a805144</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="26" t="inlineStr">
+      <c r="A58" s="20" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B58" s="35" t="inlineStr">
+      <c r="B58" s="29" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C58" s="28" t="inlineStr">
+      <c r="C58" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D58" s="29" t="inlineStr">
+      <c r="D58" s="23" t="inlineStr">
         <is>
           <t>Ajout des notices IFU HOB Biotech BioCLIA (127 produits).</t>
         </is>
       </c>
-      <c r="E58" s="30" t="inlineStr">
+      <c r="E58" s="24" t="inlineStr">
         <is>
           <t>38c74fc</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="21" t="inlineStr">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B59" s="34" t="inlineStr">
+      <c r="B59" s="28" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C59" s="23" t="inlineStr">
+      <c r="C59" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D59" s="24" t="inlineStr">
+      <c r="D59" s="18" t="inlineStr">
         <is>
           <t>Ajout de 15 notices ERBA et Generic Assays depuis les sites fabricants.</t>
         </is>
       </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="E59" s="19" t="inlineStr">
         <is>
           <t>fb86426</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="26" t="inlineStr">
+      <c r="A60" s="20" t="inlineStr">
         <is>
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="B60" s="32" t="inlineStr">
+      <c r="B60" s="26" t="inlineStr">
         <is>
           <t>Donnees/Catalogue</t>
         </is>
       </c>
-      <c r="C60" s="28" t="inlineStr">
+      <c r="C60" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D60" s="29" t="inlineStr">
+      <c r="D60" s="23" t="inlineStr">
         <is>
           <t>Ajout de notices et d'images produits, suppression des references abandonnees.</t>
         </is>
       </c>
-      <c r="E60" s="30" t="inlineStr">
+      <c r="E60" s="24" t="inlineStr">
         <is>
           <t>dba5fc5</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="21" t="inlineStr">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B61" s="31" t="inlineStr">
+      <c r="B61" s="25" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C61" s="23" t="inlineStr">
+      <c r="C61" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D61" s="24" t="inlineStr">
+      <c r="D61" s="18" t="inlineStr">
         <is>
           <t>Corrections de bugs, ajout d'images produits et optimisation des performances du catalogue.</t>
         </is>
       </c>
-      <c r="E61" s="25" t="inlineStr">
+      <c r="E61" s="19" t="inlineStr">
         <is>
           <t>bdc9cfa</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="26" t="inlineStr">
+      <c r="A62" s="20" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B62" s="36" t="inlineStr">
+      <c r="B62" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C62" s="28" t="inlineStr">
+      <c r="C62" s="22" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D62" s="29" t="inlineStr">
+      <c r="D62" s="23" t="inlineStr">
         <is>
           <t>Correction du crash du panneau admin sur l'onglet « Tous les comptes » + bouton d'actualisation.</t>
         </is>
       </c>
-      <c r="E62" s="30" t="inlineStr">
+      <c r="E62" s="24" t="inlineStr">
         <is>
           <t>c3401ea</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="21" t="inlineStr">
+      <c r="A63" s="15" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B63" s="33" t="inlineStr">
+      <c r="B63" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C63" s="23" t="inlineStr">
+      <c r="C63" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D63" s="24" t="inlineStr">
+      <c r="D63" s="18" t="inlineStr">
         <is>
           <t>Retrait du telechargement Excel lors de l'envoi d'un devis.</t>
         </is>
       </c>
-      <c r="E63" s="25" t="inlineStr">
+      <c r="E63" s="19" t="inlineStr">
         <is>
           <t>6c6faf6</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="26" t="inlineStr">
+    <row r="64" ht="27" customHeight="1" s="36">
+      <c r="A64" s="20" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B64" s="36" t="inlineStr">
+      <c r="B64" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C64" s="28" t="inlineStr">
+      <c r="C64" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D64" s="29" t="inlineStr">
+      <c r="D64" s="23" t="inlineStr">
         <is>
           <t>Correction d'une violation des Rules of Hooks dans ReactifsContent (useMemo avant retours conditionnels).</t>
         </is>
       </c>
-      <c r="E64" s="30" t="inlineStr">
+      <c r="E64" s="24" t="inlineStr">
         <is>
           <t>bfe3ba3</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="21" t="inlineStr">
+      <c r="A65" s="15" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B65" s="31" t="inlineStr">
+      <c r="B65" s="25" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C65" s="23" t="inlineStr">
+      <c r="C65" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D65" s="24" t="inlineStr">
+      <c r="D65" s="18" t="inlineStr">
         <is>
           <t>Mise a jour des images IFI Manuel et correction de l'affichage des logos dans les cartes produits.</t>
         </is>
       </c>
-      <c r="E65" s="25" t="inlineStr">
+      <c r="E65" s="19" t="inlineStr">
         <is>
           <t>6ea322b</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="26" t="inlineStr">
+      <c r="A66" s="20" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B66" s="32" t="inlineStr">
+      <c r="B66" s="26" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C66" s="28" t="inlineStr">
+      <c r="C66" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D66" s="29" t="inlineStr">
+      <c r="D66" s="23" t="inlineStr">
         <is>
           <t>Mise a jour d'images produits et renommage de la sous-categorie Allergie BioCLIA.</t>
         </is>
       </c>
-      <c r="E66" s="30" t="inlineStr">
+      <c r="E66" s="24" t="inlineStr">
         <is>
           <t>1e775af</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="21" t="inlineStr">
+    <row r="67" ht="27" customHeight="1" s="36">
+      <c r="A67" s="15" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B67" s="33" t="inlineStr">
+      <c r="B67" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C67" s="23" t="inlineStr">
+      <c r="C67" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D67" s="24" t="inlineStr">
+      <c r="D67" s="18" t="inlineStr">
         <is>
           <t>Masquage de la barre de filtres en navigation par sous-categorie + correction de l'image LINE ANA 12.</t>
         </is>
       </c>
-      <c r="E67" s="25" t="inlineStr">
+      <c r="E67" s="19" t="inlineStr">
         <is>
           <t>cf78205</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="26" t="inlineStr">
+      <c r="A68" s="20" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B68" s="36" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C68" s="28" t="inlineStr">
+      <c r="C68" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D68" s="29" t="inlineStr">
+      <c r="D68" s="23" t="inlineStr">
         <is>
           <t>Correction des references produits en double dans la recherche et des libelles SECTION_DISPLAY.</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E68" s="24" t="inlineStr">
         <is>
           <t>a8b73a6</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="21" t="inlineStr">
+      <c r="A69" s="15" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B69" s="31" t="inlineStr">
+      <c r="B69" s="25" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C69" s="23" t="inlineStr">
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D69" s="24" t="inlineStr">
+      <c r="D69" s="18" t="inlineStr">
         <is>
           <t>Correction du fil d'Ariane dans le catalogue reactifs.</t>
         </is>
       </c>
-      <c r="E69" s="25" t="inlineStr">
+      <c r="E69" s="19" t="inlineStr">
         <is>
           <t>3ee0a1d</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="26" t="inlineStr">
+      <c r="A70" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B70" s="35" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C70" s="28" t="inlineStr">
+      <c r="C70" s="22" t="inlineStr">
         <is>
           <t>Partenaires</t>
         </is>
       </c>
-      <c r="D70" s="29" t="inlineStr">
+      <c r="D70" s="23" t="inlineStr">
         <is>
           <t>Ajout de la page « Nos Partenaires » avec 5 logos partenaires.</t>
         </is>
       </c>
-      <c r="E70" s="30" t="inlineStr">
+      <c r="E70" s="24" t="inlineStr">
         <is>
           <t>853ba17</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="21" t="inlineStr">
+      <c r="A71" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B71" s="33" t="inlineStr">
+      <c r="B71" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C71" s="23" t="inlineStr">
+      <c r="C71" s="17" t="inlineStr">
         <is>
           <t>Partenaires</t>
         </is>
       </c>
-      <c r="D71" s="24" t="inlineStr">
+      <c r="D71" s="18" t="inlineStr">
         <is>
           <t>Mise a jour des logos partenaires Medipan et Generic Assays.</t>
         </is>
       </c>
-      <c r="E71" s="25" t="inlineStr">
+      <c r="E71" s="19" t="inlineStr">
         <is>
           <t>91c0021</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="26" t="inlineStr">
+      <c r="A72" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B72" s="39" t="inlineStr">
+      <c r="B72" s="33" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="C72" s="28" t="inlineStr">
+      <c r="C72" s="22" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D72" s="29" t="inlineStr">
+      <c r="D72" s="23" t="inlineStr">
         <is>
           <t>Connexion desormais requise pour envoyer une demande de devis.</t>
         </is>
       </c>
-      <c r="E72" s="30" t="inlineStr">
+      <c r="E72" s="24" t="inlineStr">
         <is>
           <t>8f9862c</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="21" t="inlineStr">
+      <c r="A73" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B73" s="38" t="inlineStr">
+      <c r="B73" s="32" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="C73" s="23" t="inlineStr">
+      <c r="C73" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D73" s="24" t="inlineStr">
+      <c r="D73" s="18" t="inlineStr">
         <is>
           <t>Durcissement du flux de devis et correction du rendu SVG des partenaires.</t>
         </is>
       </c>
-      <c r="E73" s="25" t="inlineStr">
+      <c r="E73" s="19" t="inlineStr">
         <is>
           <t>973cc22</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="26" t="inlineStr">
+      <c r="A74" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B74" s="27" t="inlineStr">
+      <c r="B74" s="21" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="C74" s="28" t="inlineStr">
+      <c r="C74" s="22" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="D74" s="29" t="inlineStr">
+      <c r="D74" s="23" t="inlineStr">
         <is>
           <t>Ajout d'un README complet (stack, structure, conventions).</t>
         </is>
       </c>
-      <c r="E74" s="30" t="inlineStr">
+      <c r="E74" s="24" t="inlineStr">
         <is>
           <t>2bf7f83</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="21" t="inlineStr">
+      <c r="A75" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B75" s="38" t="inlineStr">
+      <c r="B75" s="32" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="C75" s="23" t="inlineStr">
+      <c r="C75" s="17" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="D75" s="24" t="inlineStr">
+      <c r="D75" s="18" t="inlineStr">
         <is>
           <t>Durcissement de la securite sur les routes API, l'authentification et les en-tetes HTTP.</t>
         </is>
       </c>
-      <c r="E75" s="25" t="inlineStr">
+      <c r="E75" s="19" t="inlineStr">
         <is>
           <t>810bbf1</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="26" t="inlineStr">
+      <c r="A76" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B76" s="39" t="inlineStr">
+      <c r="B76" s="33" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="C76" s="28" t="inlineStr">
+      <c r="C76" s="22" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="D76" s="29" t="inlineStr">
+      <c r="D76" s="23" t="inlineStr">
         <is>
           <t>Autorisation de *.vercel.app et du meme hote comme origine dans le filtre CSRF.</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E76" s="24" t="inlineStr">
         <is>
           <t>fc497d3</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="21" t="inlineStr">
+      <c r="A77" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B77" s="31" t="inlineStr">
+      <c r="B77" s="25" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C77" s="23" t="inlineStr">
+      <c r="C77" s="17" t="inlineStr">
         <is>
           <t>Compte/Auth</t>
         </is>
       </c>
-      <c r="D77" s="24" t="inlineStr">
+      <c r="D77" s="18" t="inlineStr">
         <is>
           <t>Correction d'une coquille dans l'adresse destinataire devis/contact (8 vers 0) pour Resend.</t>
         </is>
       </c>
-      <c r="E77" s="25" t="inlineStr">
+      <c r="E77" s="19" t="inlineStr">
         <is>
           <t>59df04b</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="26" t="inlineStr">
+      <c r="A78" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B78" s="32" t="inlineStr">
+      <c r="B78" s="26" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C78" s="28" t="inlineStr">
+      <c r="C78" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D78" s="29" t="inlineStr">
+      <c r="D78" s="23" t="inlineStr">
         <is>
           <t>Mise a jour d'images du catalogue et de l'URL du partenaire ERBA.</t>
         </is>
       </c>
-      <c r="E78" s="30" t="inlineStr">
+      <c r="E78" s="24" t="inlineStr">
         <is>
           <t>dc32419</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="21" t="inlineStr">
+      <c r="A79" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B79" s="31" t="inlineStr">
+      <c r="B79" s="25" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C79" s="23" t="inlineStr">
+      <c r="C79" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D79" s="24" t="inlineStr">
+      <c r="D79" s="18" t="inlineStr">
         <is>
           <t>Restauration des images d'origine pour les sous-categories Auto-Immunite non-CLIA.</t>
         </is>
       </c>
-      <c r="E79" s="25" t="inlineStr">
+      <c r="E79" s="19" t="inlineStr">
         <is>
           <t>7d13ace</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="26" t="inlineStr">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B80" s="36" t="inlineStr">
+      <c r="B80" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C80" s="28" t="inlineStr">
+      <c r="C80" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D80" s="29" t="inlineStr">
+      <c r="D80" s="23" t="inlineStr">
         <is>
           <t>Correction du libelle de categorie perime dans le fil d'Ariane (navigation SPA).</t>
         </is>
       </c>
-      <c r="E80" s="30" t="inlineStr">
+      <c r="E80" s="24" t="inlineStr">
         <is>
           <t>4e9524a</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="21" t="inlineStr">
+      <c r="A81" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B81" s="33" t="inlineStr">
+      <c r="B81" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C81" s="23" t="inlineStr">
+      <c r="C81" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D81" s="24" t="inlineStr">
+      <c r="D81" s="18" t="inlineStr">
         <is>
           <t>Mise a jour des images et du conditionnement des sous-categories allergie.</t>
         </is>
       </c>
-      <c r="E81" s="25" t="inlineStr">
+      <c r="E81" s="19" t="inlineStr">
         <is>
           <t>e5bd8c7</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="26" t="inlineStr">
+      <c r="A82" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B82" s="36" t="inlineStr">
+      <c r="B82" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C82" s="28" t="inlineStr">
+      <c r="C82" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D82" s="29" t="inlineStr">
+      <c r="D82" s="23" t="inlineStr">
         <is>
           <t>Correction de la casse du conditionnement CLIA (« test » vers « Tests »).</t>
         </is>
       </c>
-      <c r="E82" s="30" t="inlineStr">
+      <c r="E82" s="24" t="inlineStr">
         <is>
           <t>25aa857</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="21" t="inlineStr">
+      <c r="A83" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B83" s="31" t="inlineStr">
+      <c r="B83" s="25" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C83" s="23" t="inlineStr">
+      <c r="C83" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D83" s="24" t="inlineStr">
+      <c r="D83" s="18" t="inlineStr">
         <is>
           <t>Correction du conditionnement de 3 consommables/controles BioCLIA.</t>
         </is>
       </c>
-      <c r="E83" s="25" t="inlineStr">
+      <c r="E83" s="19" t="inlineStr">
         <is>
           <t>959c697</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="26" t="inlineStr">
+      <c r="A84" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B84" s="35" t="inlineStr">
+      <c r="B84" s="29" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C84" s="28" t="inlineStr">
+      <c r="C84" s="22" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="D84" s="29" t="inlineStr">
+      <c r="D84" s="23" t="inlineStr">
         <is>
           <t>Ajout d'une page d'atterrissage par categorie au catalogue equipements.</t>
         </is>
       </c>
-      <c r="E84" s="30" t="inlineStr">
+      <c r="E84" s="24" t="inlineStr">
         <is>
           <t>c68e5c8</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="21" t="inlineStr">
+      <c r="A85" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B85" s="33" t="inlineStr">
+      <c r="B85" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C85" s="23" t="inlineStr">
+      <c r="C85" s="17" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="D85" s="24" t="inlineStr">
+      <c r="D85" s="18" t="inlineStr">
         <is>
           <t>Vue grille par defaut pour le catalogue equipements.</t>
         </is>
       </c>
-      <c r="E85" s="25" t="inlineStr">
+      <c r="E85" s="19" t="inlineStr">
         <is>
           <t>d9f3340</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="26" t="inlineStr">
+      <c r="A86" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B86" s="35" t="inlineStr">
+      <c r="B86" s="29" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C86" s="28" t="inlineStr">
+      <c r="C86" s="22" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="D86" s="29" t="inlineStr">
+      <c r="D86" s="23" t="inlineStr">
         <is>
           <t>Ajout des blocs « Points forts » aux pages categorie equipements.</t>
         </is>
       </c>
-      <c r="E86" s="30" t="inlineStr">
+      <c r="E86" s="24" t="inlineStr">
         <is>
           <t>e6e9a5a</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="21" t="inlineStr">
+      <c r="A87" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B87" s="33" t="inlineStr">
+      <c r="B87" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C87" s="23" t="inlineStr">
+      <c r="C87" s="17" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="D87" s="24" t="inlineStr">
+      <c r="D87" s="18" t="inlineStr">
         <is>
           <t>Masquage de la barre de filtres et des libelles de section (navigation par categorie).</t>
         </is>
       </c>
-      <c r="E87" s="25" t="inlineStr">
+      <c r="E87" s="19" t="inlineStr">
         <is>
           <t>5f4828b</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="26" t="inlineStr">
+      <c r="A88" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B88" s="37" t="inlineStr">
+      <c r="B88" s="31" t="inlineStr">
         <is>
           <t>Refonte/Design</t>
         </is>
       </c>
-      <c r="C88" s="28" t="inlineStr">
+      <c r="C88" s="22" t="inlineStr">
         <is>
           <t>Transverse</t>
         </is>
       </c>
-      <c r="D88" s="29" t="inlineStr">
+      <c r="D88" s="23" t="inlineStr">
         <is>
           <t>Ajout d'animations d'apparition au defilement sur toutes les pages.</t>
         </is>
       </c>
-      <c r="E88" s="30" t="inlineStr">
+      <c r="E88" s="24" t="inlineStr">
         <is>
           <t>d859f09</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="21" t="inlineStr">
+      <c r="A89" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B89" s="40" t="inlineStr">
+      <c r="B89" s="34" t="inlineStr">
         <is>
           <t>Refonte/Design</t>
         </is>
       </c>
-      <c r="C89" s="23" t="inlineStr">
+      <c r="C89" s="17" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="D89" s="24" t="inlineStr">
+      <c r="D89" s="18" t="inlineStr">
         <is>
           <t>Banniere biochimie : texte d'intro au-dessus des cartes, cartes sur une ligne de 4 colonnes.</t>
         </is>
       </c>
-      <c r="E89" s="25" t="inlineStr">
+      <c r="E89" s="19" t="inlineStr">
         <is>
           <t>3ad2818</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="26" t="inlineStr">
+      <c r="A90" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B90" s="37" t="inlineStr">
+      <c r="B90" s="31" t="inlineStr">
         <is>
           <t>Refonte/Design</t>
         </is>
       </c>
-      <c r="C90" s="28" t="inlineStr">
+      <c r="C90" s="22" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="D90" s="29" t="inlineStr">
+      <c r="D90" s="23" t="inlineStr">
         <is>
           <t>Centrage du texte d'introduction dans la banniere biochimie.</t>
         </is>
       </c>
-      <c r="E90" s="30" t="inlineStr">
+      <c r="E90" s="24" t="inlineStr">
         <is>
           <t>c03ba3d</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="21" t="inlineStr">
+      <c r="A91" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B91" s="33" t="inlineStr">
+      <c r="B91" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C91" s="23" t="inlineStr">
+      <c r="C91" s="17" t="inlineStr">
         <is>
           <t>Design/UI</t>
         </is>
       </c>
-      <c r="D91" s="24" t="inlineStr">
+      <c r="D91" s="18" t="inlineStr">
         <is>
           <t>Bouton « Haut de page » : forme pilule avec texte et animation permanente.</t>
         </is>
       </c>
-      <c r="E91" s="25" t="inlineStr">
+      <c r="E91" s="19" t="inlineStr">
         <is>
           <t>f83d0b3</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="26" t="inlineStr">
+      <c r="A92" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B92" s="27" t="inlineStr">
+      <c r="B92" s="21" t="inlineStr">
         <is>
           <t>Infra/Chore</t>
         </is>
       </c>
-      <c r="C92" s="28" t="inlineStr">
+      <c r="C92" s="22" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D92" s="29" t="inlineStr">
+      <c r="D92" s="23" t="inlineStr">
         <is>
           <t>Blocage de l'auto-deploiement Vercel sur la branche homepage-test.</t>
         </is>
       </c>
-      <c r="E92" s="30" t="inlineStr">
+      <c r="E92" s="24" t="inlineStr">
         <is>
           <t>3c72f01</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="21" t="inlineStr">
+      <c r="A93" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B93" s="40" t="inlineStr">
+      <c r="B93" s="34" t="inlineStr">
         <is>
           <t>Refonte/Design</t>
         </is>
       </c>
-      <c r="C93" s="23" t="inlineStr">
+      <c r="C93" s="17" t="inlineStr">
         <is>
           <t>Accueil</t>
         </is>
       </c>
-      <c r="D93" s="24" t="inlineStr">
+      <c r="D93" s="18" t="inlineStr">
         <is>
           <t>Refonte de la page d'accueil avec une mise en page cinematique inspiree d'Apple.</t>
         </is>
       </c>
-      <c r="E93" s="25" t="inlineStr">
+      <c r="E93" s="19" t="inlineStr">
         <is>
           <t>4c7c2ea</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="26" t="inlineStr">
+      <c r="A94" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B94" s="37" t="inlineStr">
+      <c r="B94" s="31" t="inlineStr">
         <is>
           <t>Refonte/Design</t>
         </is>
       </c>
-      <c r="C94" s="28" t="inlineStr">
+      <c r="C94" s="22" t="inlineStr">
         <is>
           <t>Transverse</t>
         </is>
       </c>
-      <c r="D94" s="29" t="inlineStr">
+      <c r="D94" s="23" t="inlineStr">
         <is>
           <t>Refonte de toutes les pages publiques avec une esthetique Apple x GSAP.</t>
         </is>
       </c>
-      <c r="E94" s="30" t="inlineStr">
+      <c r="E94" s="24" t="inlineStr">
         <is>
           <t>eba733e</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="21" t="inlineStr">
+      <c r="A95" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B95" s="40" t="inlineStr">
+      <c r="B95" s="34" t="inlineStr">
         <is>
           <t>Refonte/Design</t>
         </is>
       </c>
-      <c r="C95" s="23" t="inlineStr">
+      <c r="C95" s="17" t="inlineStr">
         <is>
           <t>Accueil</t>
         </is>
       </c>
-      <c r="D95" s="24" t="inlineStr">
+      <c r="D95" s="18" t="inlineStr">
         <is>
           <t>Ajout d'une vitrine horizontale pilotee au defilement + parallaxe sur l'accueil.</t>
         </is>
       </c>
-      <c r="E95" s="25" t="inlineStr">
+      <c r="E95" s="19" t="inlineStr">
         <is>
           <t>f84e9ba</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="26" t="inlineStr">
+      <c r="A96" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B96" s="36" t="inlineStr">
+      <c r="B96" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C96" s="28" t="inlineStr">
+      <c r="C96" s="22" t="inlineStr">
         <is>
           <t>Accueil</t>
         </is>
       </c>
-      <c r="D96" s="29" t="inlineStr">
+      <c r="D96" s="23" t="inlineStr">
         <is>
           <t>Correction de l'epinglage (sticky) de PinnedShowcase.</t>
         </is>
       </c>
-      <c r="E96" s="30" t="inlineStr">
+      <c r="E96" s="24" t="inlineStr">
         <is>
           <t>3bda32b</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="21" t="inlineStr">
+      <c r="A97" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B97" s="33" t="inlineStr">
+      <c r="B97" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C97" s="23" t="inlineStr">
+      <c r="C97" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D97" s="24" t="inlineStr">
+      <c r="D97" s="18" t="inlineStr">
         <is>
           <t>Reutilisation de PinnedShowcase sur les deux pages d'atterrissage catalogue.</t>
         </is>
       </c>
-      <c r="E97" s="25" t="inlineStr">
+      <c r="E97" s="19" t="inlineStr">
         <is>
           <t>99df951</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="26" t="inlineStr">
+      <c r="A98" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B98" s="32" t="inlineStr">
+      <c r="B98" s="26" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C98" s="28" t="inlineStr">
+      <c r="C98" s="22" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="D98" s="29" t="inlineStr">
+      <c r="D98" s="23" t="inlineStr">
         <is>
           <t>Retrait de la vitrine epinglee de la page Equipements.</t>
         </is>
       </c>
-      <c r="E98" s="30" t="inlineStr">
+      <c r="E98" s="24" t="inlineStr">
         <is>
           <t>aa9a87e</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="21" t="inlineStr">
+      <c r="A99" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B99" s="33" t="inlineStr">
+      <c r="B99" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C99" s="23" t="inlineStr">
+      <c r="C99" s="17" t="inlineStr">
         <is>
           <t>Reactifs</t>
         </is>
       </c>
-      <c r="D99" s="24" t="inlineStr">
+      <c r="D99" s="18" t="inlineStr">
         <is>
           <t>Retrait de la vitrine epinglee de la page Reactifs.</t>
         </is>
       </c>
-      <c r="E99" s="25" t="inlineStr">
+      <c r="E99" s="19" t="inlineStr">
         <is>
           <t>3c4b635</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="26" t="inlineStr">
+      <c r="A100" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B100" s="37" t="inlineStr">
+      <c r="B100" s="31" t="inlineStr">
         <is>
           <t>Refonte/Design</t>
         </is>
       </c>
-      <c r="C100" s="28" t="inlineStr">
+      <c r="C100" s="22" t="inlineStr">
         <is>
           <t>Transverse</t>
         </is>
       </c>
-      <c r="D100" s="29" t="inlineStr">
+      <c r="D100" s="23" t="inlineStr">
         <is>
           <t>Lissage des animations au defilement par interpolation (lerp).</t>
         </is>
       </c>
-      <c r="E100" s="30" t="inlineStr">
+      <c r="E100" s="24" t="inlineStr">
         <is>
           <t>7429cde</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="21" t="inlineStr">
+      <c r="A101" s="15" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B101" s="40" t="inlineStr">
+      <c r="B101" s="34" t="inlineStr">
         <is>
           <t>Refonte/Design</t>
         </is>
       </c>
-      <c r="C101" s="23" t="inlineStr">
+      <c r="C101" s="17" t="inlineStr">
         <is>
           <t>Design/UI</t>
         </is>
       </c>
-      <c r="D101" s="24" t="inlineStr">
+      <c r="D101" s="18" t="inlineStr">
         <is>
           <t>Ajout d'un repli mobile/tablette a PinnedShowcase (&lt; 900px).</t>
         </is>
       </c>
-      <c r="E101" s="25" t="inlineStr">
+      <c r="E101" s="19" t="inlineStr">
         <is>
           <t>685af63</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="26" t="inlineStr">
+      <c r="A102" s="20" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B102" s="36" t="inlineStr">
+      <c r="B102" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C102" s="28" t="inlineStr">
+      <c r="C102" s="22" t="inlineStr">
         <is>
           <t>Transverse</t>
         </is>
       </c>
-      <c r="D102" s="29" t="inlineStr">
+      <c r="D102" s="23" t="inlineStr">
         <is>
           <t>Restauration des textes d'origine sur les pages refondues.</t>
         </is>
       </c>
-      <c r="E102" s="30" t="inlineStr">
+      <c r="E102" s="24" t="inlineStr">
         <is>
           <t>54483e9</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="21" t="inlineStr">
+      <c r="A103" s="15" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B103" s="38" t="inlineStr">
+      <c r="B103" s="32" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="C103" s="23" t="inlineStr">
+      <c r="C103" s="17" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="D103" s="24" t="inlineStr">
+      <c r="D103" s="18" t="inlineStr">
         <is>
           <t>Assainissement du HTML du blog avec DOMPurify (correction d'une faille XSS stockee).</t>
         </is>
       </c>
-      <c r="E103" s="25" t="inlineStr">
+      <c r="E103" s="19" t="inlineStr">
         <is>
           <t>9f8c104</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="26" t="inlineStr">
+      <c r="A104" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B104" s="36" t="inlineStr">
+      <c r="B104" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C104" s="28" t="inlineStr">
+      <c r="C104" s="22" t="inlineStr">
         <is>
           <t>Design/UI</t>
         </is>
       </c>
-      <c r="D104" s="29" t="inlineStr">
+      <c r="D104" s="23" t="inlineStr">
         <is>
           <t>Correction de problemes responsive sur PinnedShowcase et CardGrid.</t>
         </is>
       </c>
-      <c r="E104" s="30" t="inlineStr">
+      <c r="E104" s="24" t="inlineStr">
         <is>
           <t>3740bfa</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="21" t="inlineStr">
+      <c r="A105" s="15" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B105" s="31" t="inlineStr">
+      <c r="B105" s="25" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C105" s="23" t="inlineStr">
+      <c r="C105" s="17" t="inlineStr">
         <is>
           <t>Design/UI</t>
         </is>
       </c>
-      <c r="D105" s="24" t="inlineStr">
+      <c r="D105" s="18" t="inlineStr">
         <is>
           <t>Correction du chevauchement de PinnedShowcase sur les petits ecrans (1080p @ 150%).</t>
         </is>
       </c>
-      <c r="E105" s="25" t="inlineStr">
+      <c r="E105" s="19" t="inlineStr">
         <is>
           <t>e1d8aaa</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="26" t="inlineStr">
+      <c r="A106" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B106" s="35" t="inlineStr">
+      <c r="B106" s="29" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C106" s="28" t="inlineStr">
+      <c r="C106" s="22" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="D106" s="29" t="inlineStr">
+      <c r="D106" s="23" t="inlineStr">
         <is>
           <t>Ajout des brochures d'equipements depuis les sites fabricants.</t>
         </is>
       </c>
-      <c r="E106" s="30" t="inlineStr">
+      <c r="E106" s="24" t="inlineStr">
         <is>
           <t>c70889b</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="21" t="inlineStr">
+      <c r="A107" s="15" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B107" s="31" t="inlineStr">
+      <c r="B107" s="25" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C107" s="23" t="inlineStr">
+      <c r="C107" s="17" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="D107" s="24" t="inlineStr">
+      <c r="D107" s="18" t="inlineStr">
         <is>
           <t>Verification des liens de brochures et retrait de l'entree morte BioCLIA 1900.</t>
         </is>
       </c>
-      <c r="E107" s="25" t="inlineStr">
+      <c r="E107" s="19" t="inlineStr">
         <is>
           <t>8118d78</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="26" t="inlineStr">
+      <c r="A108" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B108" s="32" t="inlineStr">
+      <c r="B108" s="26" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C108" s="28" t="inlineStr">
+      <c r="C108" s="22" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D108" s="29" t="inlineStr">
+      <c r="D108" s="23" t="inlineStr">
         <is>
           <t>Alignement du style des boutons de brochure sur ceux des notices reactifs.</t>
         </is>
       </c>
-      <c r="E108" s="30" t="inlineStr">
+      <c r="E108" s="24" t="inlineStr">
         <is>
           <t>25df8dd</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="21" t="inlineStr">
+      <c r="A109" s="15" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B109" s="33" t="inlineStr">
+      <c r="B109" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C109" s="23" t="inlineStr">
+      <c r="C109" s="17" t="inlineStr">
         <is>
           <t>Design/UI</t>
         </is>
       </c>
-      <c r="D109" s="24" t="inlineStr">
+      <c r="D109" s="18" t="inlineStr">
         <is>
           <t>Pied de page : saut de ligne entre le libelle SAV et le numero de telephone.</t>
         </is>
       </c>
-      <c r="E109" s="25" t="inlineStr">
+      <c r="E109" s="19" t="inlineStr">
         <is>
           <t>489eb42</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="26" t="inlineStr">
+      <c r="A110" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B110" s="32" t="inlineStr">
+      <c r="B110" s="26" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C110" s="28" t="inlineStr">
+      <c r="C110" s="22" t="inlineStr">
         <is>
           <t>Equipements</t>
         </is>
       </c>
-      <c r="D110" s="29" t="inlineStr">
+      <c r="D110" s="23" t="inlineStr">
         <is>
           <t>Renommage de la categorie « Auto-Immunite » en « Auto-Immunite / Allergie ».</t>
         </is>
       </c>
-      <c r="E110" s="30" t="inlineStr">
+      <c r="E110" s="24" t="inlineStr">
         <is>
           <t>391d1f4</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="21" t="inlineStr">
+      <c r="A111" s="15" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B111" s="38" t="inlineStr">
+      <c r="B111" s="32" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="C111" s="23" t="inlineStr">
+      <c r="C111" s="17" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="D111" s="24" t="inlineStr">
+      <c r="D111" s="18" t="inlineStr">
         <is>
           <t>Ajout de routes API securisees, des types blog, d'un helper Resend et de scripts utilitaires.</t>
         </is>
       </c>
-      <c r="E111" s="25" t="inlineStr">
+      <c r="E111" s="19" t="inlineStr">
         <is>
           <t>74147c3</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="26" t="inlineStr">
+      <c r="A112" s="20" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B112" s="27" t="inlineStr">
+      <c r="B112" s="21" t="inlineStr">
         <is>
           <t>Infra/Chore</t>
         </is>
       </c>
-      <c r="C112" s="28" t="inlineStr">
+      <c r="C112" s="22" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D112" s="29" t="inlineStr">
+      <c r="D112" s="23" t="inlineStr">
         <is>
           <t>Retrait du blocage de deploiement homepage-test dans vercel.json.</t>
         </is>
       </c>
-      <c r="E112" s="30" t="inlineStr">
+      <c r="E112" s="24" t="inlineStr">
         <is>
           <t>cad1d5a</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="21" t="inlineStr">
+      <c r="A113" s="15" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B113" s="22" t="inlineStr">
+      <c r="B113" s="16" t="inlineStr">
         <is>
           <t>Infra/Chore</t>
         </is>
       </c>
-      <c r="C113" s="23" t="inlineStr">
+      <c r="C113" s="17" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D113" s="24" t="inlineStr">
+      <c r="D113" s="18" t="inlineStr">
         <is>
           <t>Fusion de la refonte (homepage-test) dans la branche principale.</t>
         </is>
       </c>
-      <c r="E113" s="25" t="inlineStr">
+      <c r="E113" s="19" t="inlineStr">
         <is>
           <t>06a33db</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="26" t="inlineStr">
+      <c r="A114" s="20" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B114" s="37" t="inlineStr">
+      <c r="B114" s="31" t="inlineStr">
         <is>
           <t>Refonte/Design</t>
         </is>
       </c>
-      <c r="C114" s="28" t="inlineStr">
+      <c r="C114" s="22" t="inlineStr">
         <is>
           <t>Design/UI</t>
         </is>
       </c>
-      <c r="D114" s="29" t="inlineStr">
+      <c r="D114" s="23" t="inlineStr">
         <is>
           <t>Remplacement du logo par le nouveau design Logo_1.svg.</t>
         </is>
       </c>
-      <c r="E114" s="30" t="inlineStr">
+      <c r="E114" s="24" t="inlineStr">
         <is>
           <t>2f00b5b</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="21" t="inlineStr">
+      <c r="A115" s="15" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="B115" s="40" t="inlineStr">
+      <c r="B115" s="34" t="inlineStr">
         <is>
           <t>Refonte/Design</t>
         </is>
       </c>
-      <c r="C115" s="23" t="inlineStr">
+      <c r="C115" s="17" t="inlineStr">
         <is>
           <t>Design/UI</t>
         </is>
       </c>
-      <c r="D115" s="24" t="inlineStr">
+      <c r="D115" s="18" t="inlineStr">
         <is>
           <t>Refonte d'une navbar interactive + ajustements UX accueil et catalogue.</t>
         </is>
       </c>
-      <c r="E115" s="25" t="inlineStr">
+      <c r="E115" s="19" t="inlineStr">
         <is>
           <t>f84618a</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="26" t="inlineStr">
+      <c r="A116" s="20" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="B116" s="36" t="inlineStr">
+      <c r="B116" s="30" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C116" s="28" t="inlineStr">
+      <c r="C116" s="22" t="inlineStr">
         <is>
           <t>Accueil</t>
         </is>
       </c>
-      <c r="D116" s="29" t="inlineStr">
+      <c r="D116" s="23" t="inlineStr">
         <is>
           <t>Correction des CTA « Voir tout » du menu Produits.</t>
         </is>
       </c>
-      <c r="E116" s="30" t="inlineStr">
+      <c r="E116" s="24" t="inlineStr">
         <is>
           <t>9cc65a1</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="21" t="inlineStr">
+      <c r="A117" s="15" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="B117" s="38" t="inlineStr">
+      <c r="B117" s="32" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="C117" s="23" t="inlineStr">
+      <c r="C117" s="17" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="D117" s="24" t="inlineStr">
+      <c r="D117" s="18" t="inlineStr">
         <is>
           <t>Durcissement de la securite : XSS bouton, brouillons prives, regles Storage.</t>
         </is>
       </c>
-      <c r="E117" s="25" t="inlineStr">
+      <c r="E117" s="19" t="inlineStr">
         <is>
           <t>a8e8907</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="26" t="inlineStr">
+      <c r="A118" s="20" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="B118" s="35" t="inlineStr">
+      <c r="B118" s="29" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C118" s="28" t="inlineStr">
+      <c r="C118" s="22" t="inlineStr">
         <is>
           <t>Accueil</t>
         </is>
       </c>
-      <c r="D118" s="29" t="inlineStr">
+      <c r="D118" s="23" t="inlineStr">
         <is>
           <t>Ajout d'une section FAQ interactive sur la page d'accueil.</t>
         </is>
       </c>
-      <c r="E118" s="30" t="inlineStr">
+      <c r="E118" s="24" t="inlineStr">
         <is>
           <t>4167521</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="21" t="inlineStr">
+      <c r="A119" s="15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="B119" s="40" t="inlineStr">
+      <c r="B119" s="34" t="inlineStr">
         <is>
           <t>Refonte/Design</t>
         </is>
       </c>
-      <c r="C119" s="23" t="inlineStr">
+      <c r="C119" s="17" t="inlineStr">
         <is>
           <t>Accueil</t>
         </is>
       </c>
-      <c r="D119" s="24" t="inlineStr">
+      <c r="D119" s="18" t="inlineStr">
         <is>
           <t>FAQ accueil : fond noir cinematique aligne sur le Hero.</t>
         </is>
       </c>
-      <c r="E119" s="25" t="inlineStr">
+      <c r="E119" s="19" t="inlineStr">
         <is>
           <t>3320818</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="26" t="inlineStr">
+      <c r="A120" s="20" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="B120" s="32" t="inlineStr">
+      <c r="B120" s="26" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C120" s="28" t="inlineStr">
+      <c r="C120" s="22" t="inlineStr">
         <is>
           <t>Partenaires</t>
         </is>
       </c>
-      <c r="D120" s="29" t="inlineStr">
+      <c r="D120" s="23" t="inlineStr">
         <is>
           <t>Mise a jour des descriptions de 3 partenaires.</t>
         </is>
       </c>
-      <c r="E120" s="30" t="inlineStr">
+      <c r="E120" s="24" t="inlineStr">
         <is>
           <t>46876b7</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="21" t="inlineStr">
+      <c r="A121" s="15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="B121" s="33" t="inlineStr">
+      <c r="B121" s="27" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C121" s="23" t="inlineStr">
+      <c r="C121" s="17" t="inlineStr">
         <is>
           <t>Catalogue</t>
         </is>
       </c>
-      <c r="D121" s="24" t="inlineStr">
+      <c r="D121" s="18" t="inlineStr">
         <is>
           <t>Badge « Auto-Immunite / Allergie » pour BioCLIA 1900 et 500.</t>
         </is>
       </c>
-      <c r="E121" s="25" t="inlineStr">
+      <c r="E121" s="19" t="inlineStr">
         <is>
           <t>ee732fe</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="26" t="inlineStr">
+      <c r="A122" s="20" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="B122" s="27" t="inlineStr">
+      <c r="B122" s="21" t="inlineStr">
         <is>
           <t>Infra/Chore</t>
         </is>
       </c>
-      <c r="C122" s="28" t="inlineStr">
+      <c r="C122" s="22" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D122" s="29" t="inlineStr">
+      <c r="D122" s="23" t="inlineStr">
         <is>
           <t>Autorisation de mcp__ide__getDiagnostics dans les permissions locales.</t>
         </is>
       </c>
-      <c r="E122" s="30" t="inlineStr">
+      <c r="E122" s="24" t="inlineStr">
         <is>
           <t>4fd5846</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="21" t="inlineStr">
+    <row r="123" ht="27" customHeight="1" s="36">
+      <c r="A123" s="15" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B123" s="34" t="inlineStr">
+      <c r="B123" s="28" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="C123" s="23" t="inlineStr">
+      <c r="C123" s="17" t="inlineStr">
         <is>
           <t>Accueil</t>
         </is>
       </c>
-      <c r="D123" s="24" t="inlineStr">
+      <c r="D123" s="18" t="inlineStr">
         <is>
           <t>Popup de choix produits sur l'accueil, guide FAQ enrichi, ouverture de fiches via ?ref= et correctifs catalogue.</t>
         </is>
       </c>
-      <c r="E123" s="25" t="inlineStr">
+      <c r="E123" s="19" t="inlineStr">
         <is>
           <t>594389d</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="26" t="inlineStr">
+      <c r="A124" s="20" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B124" s="32" t="inlineStr">
+      <c r="B124" s="26" t="inlineStr">
         <is>
           <t>Amelioration</t>
         </is>
       </c>
-      <c r="C124" s="28" t="inlineStr">
+      <c r="C124" s="22" t="inlineStr">
         <is>
           <t>Transverse</t>
         </is>
       </c>
-      <c r="D124" s="29" t="inlineStr">
+      <c r="D124" s="23" t="inlineStr">
         <is>
           <t>Page A propos : coordonnees Commercial/SAV, champs de devis obligatoires, accents reactifs.</t>
         </is>
       </c>
-      <c r="E124" s="30" t="inlineStr">
+      <c r="E124" s="24" t="inlineStr">
         <is>
           <t>567d2f7</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="21" t="inlineStr">
+      <c r="A125" s="15" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B125" s="22" t="inlineStr">
+      <c r="B125" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="C125" s="23" t="inlineStr">
+      <c r="C125" s="17" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="D125" s="24" t="inlineStr">
+      <c r="D125" s="18" t="inlineStr">
         <is>
           <t>Ajout de CLAUDE.md, d'un script de publication d'article et des permissions locales.</t>
         </is>
       </c>
-      <c r="E125" s="25" t="inlineStr">
+      <c r="E125" s="19" t="inlineStr">
         <is>
           <t>9556515</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="26" t="inlineStr">
+      <c r="A126" s="20" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B126" s="27" t="inlineStr">
+      <c r="B126" s="21" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="C126" s="28" t="inlineStr">
+      <c r="C126" s="22" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="D126" s="29" t="inlineStr">
+      <c r="D126" s="23" t="inlineStr">
         <is>
           <t>Consignation de la traduction FR de l'article CytoBead ANA 2 dans le rapport.</t>
         </is>
       </c>
-      <c r="E126" s="30" t="inlineStr">
+      <c r="E126" s="24" t="inlineStr">
         <is>
           <t>10f0cbb</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="21" t="inlineStr">
+      <c r="A127" s="15" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B127" s="22" t="inlineStr">
+      <c r="B127" s="16" t="inlineStr">
         <is>
           <t>Infra/Chore</t>
         </is>
       </c>
-      <c r="C127" s="23" t="inlineStr">
+      <c r="C127" s="17" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D127" s="24" t="inlineStr">
+      <c r="D127" s="18" t="inlineStr">
         <is>
           <t>Mise a jour des permissions locales Claude.</t>
         </is>
       </c>
-      <c r="E127" s="25" t="inlineStr">
+      <c r="E127" s="19" t="inlineStr">
         <is>
           <t>b95e5cc</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="26" t="inlineStr">
+      <c r="A128" s="20" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B128" s="27" t="inlineStr">
+      <c r="B128" s="21" t="inlineStr">
         <is>
           <t>Infra/Chore</t>
         </is>
       </c>
-      <c r="C128" s="28" t="inlineStr">
+      <c r="C128" s="22" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D128" s="29" t="inlineStr">
+      <c r="D128" s="23" t="inlineStr">
         <is>
           <t>Ignorance des fichiers-verrous temporaires d'Office (~$*) dans git.</t>
         </is>
       </c>
-      <c r="E128" s="30" t="inlineStr">
+      <c r="E128" s="24" t="inlineStr">
         <is>
           <t>0f72b3e</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="21" t="inlineStr">
+      <c r="A129" s="15" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B129" s="38" t="inlineStr">
+      <c r="B129" s="32" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="C129" s="23" t="inlineStr">
+      <c r="C129" s="17" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="D129" s="24" t="inlineStr">
+      <c r="D129" s="18" t="inlineStr">
         <is>
           <t>Durcissements de securite (anti-tabnabbing, emailVerified) + audit consigne.</t>
         </is>
       </c>
-      <c r="E129" s="25" t="inlineStr">
+      <c r="E129" s="19" t="inlineStr">
         <is>
           <t>4ab3746</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="26" t="inlineStr">
+      <c r="A130" s="20" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B130" s="39" t="inlineStr">
+      <c r="B130" s="33" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="C130" s="28" t="inlineStr">
+      <c r="C130" s="22" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="D130" s="29" t="inlineStr">
+      <c r="D130" s="23" t="inlineStr">
         <is>
           <t>Permissions locales + investigation des vulnerabilites de dependances consignee.</t>
         </is>
       </c>
-      <c r="E130" s="30" t="inlineStr">
+      <c r="E130" s="24" t="inlineStr">
         <is>
           <t>30d917d</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="21" t="inlineStr">
+      <c r="A131" s="15" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B131" s="38" t="inlineStr">
+      <c r="B131" s="32" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="C131" s="23" t="inlineStr">
+      <c r="C131" s="17" t="inlineStr">
         <is>
           <t>Securite</t>
         </is>
       </c>
-      <c r="D131" s="24" t="inlineStr">
+      <c r="D131" s="18" t="inlineStr">
         <is>
           <t>Montee firebase-admin 13 vers 14 (corrige 2 vulnerabilites) + engines node &gt;= 22.</t>
         </is>
       </c>
-      <c r="E131" s="25" t="inlineStr">
+      <c r="E131" s="19" t="inlineStr">
         <is>
           <t>4ebfe5f</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="26" t="inlineStr">
+      <c r="A132" s="20" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B132" s="27" t="inlineStr">
+      <c r="B132" s="21" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="C132" s="28" t="inlineStr">
+      <c r="C132" s="22" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="D132" s="29" t="inlineStr">
+      <c r="D132" s="23" t="inlineStr">
         <is>
           <t>Consignation de l'application de firebase-admin@14 (10 vers 8 vulnerabilites).</t>
         </is>
       </c>
-      <c r="E132" s="30" t="inlineStr">
+      <c r="E132" s="24" t="inlineStr">
         <is>
           <t>f769da4</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="21" t="inlineStr">
+      <c r="A133" s="15" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B133" s="22" t="inlineStr">
+      <c r="B133" s="16" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="C133" s="23" t="inlineStr">
+      <c r="C133" s="17" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="D133" s="24" t="inlineStr">
+      <c r="D133" s="18" t="inlineStr">
         <is>
           <t>Consignation du deploiement firebase-admin@14 confirme en production.</t>
         </is>
       </c>
-      <c r="E133" s="25" t="inlineStr">
+      <c r="E133" s="19" t="inlineStr">
         <is>
           <t>303b8f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B134" s="21" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="C134" s="22" t="inlineStr">
+        <is>
+          <t>Equipements</t>
+        </is>
+      </c>
+      <c r="D134" s="23" t="inlineStr">
+        <is>
+          <t>Ajout de 2 analyseurs ERBA (LISA SCAN, LISA WASH) et creation de la categorie Immunologie au catalogue equipements.</t>
+        </is>
+      </c>
+      <c r="E134" s="24" t="inlineStr">
+        <is>
+          <t>38ba790</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B135" s="16" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
+        <is>
+          <t>Equipements</t>
+        </is>
+      </c>
+      <c r="D135" s="18" t="inlineStr">
+        <is>
+          <t>Conditionnement reel des analyseurs ELISA + liaison des reactifs compatibles de LISA SCAN (section Auto-Immunite -ELISA Manuel).</t>
+        </is>
+      </c>
+      <c r="E135" s="19" t="inlineStr">
+        <is>
+          <t>1f7f533</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B136" s="21" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="C136" s="22" t="inlineStr">
+        <is>
+          <t>Equipements</t>
+        </is>
+      </c>
+      <c r="D136" s="23" t="inlineStr">
+        <is>
+          <t>Correction typo du champ conditionnement des analyseurs ELISA (apostrophe + accent).</t>
+        </is>
+      </c>
+      <c r="E136" s="24" t="inlineStr">
+        <is>
+          <t>7712c9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B137" s="16" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="C137" s="17" t="inlineStr">
+        <is>
+          <t>Equipements</t>
+        </is>
+      </c>
+      <c r="D137" s="18" t="inlineStr">
+        <is>
+          <t>Ajout de la categorie Immunologie dans le guide intelligent (LISA SCAN + LISA WASH).</t>
+        </is>
+      </c>
+      <c r="E137" s="19" t="inlineStr">
+        <is>
+          <t>2219a79</t>
         </is>
       </c>
     </row>
@@ -4658,6 +4732,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.2362204724409449" right="0.2362204724409449" top="0.1968503937007874" bottom="0.1968503937007874" header="0.3149606299212598" footer="0"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="97" fitToHeight="0" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>